--- a/backend/technoeconomic-inputs/technoeconomic-inputs-template.xlsx
+++ b/backend/technoeconomic-inputs/technoeconomic-inputs-template.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8954da175e61d5af/Escritorio/IIT/NICCP-AI/backend/technoeconomic-inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="10_ncr:20000_{4F2B366B-AA2F-4F18-863E-957538EF6F0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B6D1F24-BD48-4AB1-8FC4-4B0902AFD3CD}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="10_ncr:20000_{4F2B366B-AA2F-4F18-863E-957538EF6F0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D7F4682-F560-46C9-9A71-8CB18347FAE0}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="E-Cooking" sheetId="2" r:id="rId1"/>
+    <sheet name="Electricity" sheetId="2" r:id="rId1"/>
     <sheet name="LPG" sheetId="1" r:id="rId2"/>
     <sheet name="Rest of subsidies or taxes" sheetId="4" r:id="rId3"/>
   </sheets>

--- a/backend/technoeconomic-inputs/technoeconomic-inputs-template.xlsx
+++ b/backend/technoeconomic-inputs/technoeconomic-inputs-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8954da175e61d5af/Escritorio/IIT/NICCP-AI/backend/technoeconomic-inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="10_ncr:20000_{4F2B366B-AA2F-4F18-863E-957538EF6F0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D7F4682-F560-46C9-9A71-8CB18347FAE0}"/>
+  <xr:revisionPtr revIDLastSave="56" documentId="10_ncr:20000_{4F2B366B-AA2F-4F18-863E-957538EF6F0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F4AD43A5-47E6-4B40-8048-7A32343975FD}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Electricity" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="49">
   <si>
     <t>Units</t>
   </si>
@@ -58,16 +58,10 @@
     <t>Outputs of the GRID techno-economic analysis</t>
   </si>
   <si>
-    <t>CAPEX</t>
-  </si>
-  <si>
     <t>Investments of generation</t>
   </si>
   <si>
     <t>Investments of the grid</t>
-  </si>
-  <si>
-    <t>OPEX</t>
   </si>
   <si>
     <t>Operation and Maintenence expenses for the generation component</t>
@@ -155,6 +149,42 @@
   </si>
   <si>
     <t>Ethanol</t>
+  </si>
+  <si>
+    <t>Revenues GRID &amp; OFF GRID</t>
+  </si>
+  <si>
+    <t>Revenues Heat</t>
+  </si>
+  <si>
+    <t>CAPEX - GRID</t>
+  </si>
+  <si>
+    <t>OPEX - GRID</t>
+  </si>
+  <si>
+    <t>CAPEX - LOCAL</t>
+  </si>
+  <si>
+    <t>OPEX - LOCAL</t>
+  </si>
+  <si>
+    <t>OPEX - OFF GRID</t>
+  </si>
+  <si>
+    <t>CAPEX - OFF GRID</t>
+  </si>
+  <si>
+    <t>CAPEX - Heat</t>
+  </si>
+  <si>
+    <t>OPEX - Heat</t>
+  </si>
+  <si>
+    <t>CAPEX - UPSTREAM</t>
+  </si>
+  <si>
+    <t>OPEX - UPSTREAM</t>
   </si>
 </sst>
 </file>
@@ -413,9 +443,6 @@
     <xf numFmtId="3" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -427,9 +454,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -462,9 +486,6 @@
     <xf numFmtId="3" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -490,6 +511,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -506,10 +536,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -788,7 +814,7 @@
         <v>2</v>
       </c>
       <c r="B1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
@@ -891,11 +917,11 @@
       </c>
     </row>
     <row r="2" spans="1:35" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="18" t="s">
-        <v>18</v>
+      <c r="A2" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>16</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>4</v>
@@ -998,118 +1024,118 @@
       </c>
     </row>
     <row r="3" spans="1:35" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="20" t="s">
-        <v>18</v>
+      <c r="B3" s="18" t="s">
+        <v>16</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="S3" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="T3" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="U3" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="V3" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="W3" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="X3" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Y3" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Z3" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AA3" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AB3" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AC3" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AD3" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AE3" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AF3" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AG3" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AH3" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AI3" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:35" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>6</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>7</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>4</v>
@@ -1213,10 +1239,10 @@
     </row>
     <row r="5" spans="1:35" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="6" t="s">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>4</v>
@@ -1319,11 +1345,11 @@
       </c>
     </row>
     <row r="6" spans="1:35" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>10</v>
+      <c r="A6" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>8</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>4</v>
@@ -1426,11 +1452,11 @@
       </c>
     </row>
     <row r="7" spans="1:35" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" s="7" t="s">
         <v>9</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>11</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>4</v>
@@ -1533,225 +1559,225 @@
       </c>
     </row>
     <row r="8" spans="1:35" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>12</v>
+      <c r="A8" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>10</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" s="10">
+        <v>11</v>
+      </c>
+      <c r="D8" s="9">
         <v>0</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L8" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M8" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N8" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O8" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="P8" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q8" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="R8" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="S8" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="T8" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="U8" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="V8" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="W8" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="X8" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Y8" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Z8" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AA8" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AB8" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AC8" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AD8" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AE8" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AF8" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AG8" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AH8" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AI8" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:35" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="20" t="s">
-        <v>18</v>
+      <c r="A9" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>16</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="S9" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="T9" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="U9" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="V9" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="W9" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="X9" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Y9" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Z9" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AA9" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AB9" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AC9" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AD9" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AE9" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AF9" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AG9" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AH9" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AI9" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:35" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" s="6" t="s">
         <v>6</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>7</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>4</v>
@@ -1855,10 +1881,10 @@
     </row>
     <row r="11" spans="1:35" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="6" t="s">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>4</v>
@@ -1961,11 +1987,11 @@
       </c>
     </row>
     <row r="12" spans="1:35" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>10</v>
+      <c r="A12" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>8</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>4</v>
@@ -2068,11 +2094,11 @@
       </c>
     </row>
     <row r="13" spans="1:35" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="7" t="s">
         <v>9</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>11</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>4</v>
@@ -2175,228 +2201,228 @@
       </c>
     </row>
     <row r="14" spans="1:35" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>12</v>
+      <c r="A14" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>10</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D14" s="10">
+        <v>11</v>
+      </c>
+      <c r="D14" s="9">
         <v>0</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K14" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L14" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M14" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N14" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O14" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="P14" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q14" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="R14" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="S14" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="T14" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="U14" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="V14" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="W14" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="X14" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Y14" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Z14" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AA14" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AB14" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AC14" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AD14" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AE14" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AF14" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AG14" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AH14" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AI14" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:35" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="F15" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="G15" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="H15" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="I15" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J15" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="K15" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="L15" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="M15" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="N15" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="O15" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="P15" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q15" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="R15" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="S15" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="T15" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="U15" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="V15" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="W15" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="X15" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="Y15" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="Z15" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="AA15" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="AB15" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="AC15" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD15" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="AE15" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="AF15" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG15" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="AH15" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="AI15" s="11" t="s">
-        <v>18</v>
+      <c r="A15" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="H15" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="I15" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J15" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="K15" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="L15" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="M15" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="N15" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="O15" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="P15" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q15" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="R15" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="S15" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="T15" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="U15" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="V15" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="W15" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="X15" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y15" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z15" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA15" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB15" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC15" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD15" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="AE15" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="AF15" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG15" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH15" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="AI15" s="10" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:35" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="23" t="s">
-        <v>3</v>
-      </c>
-      <c r="B16" s="18" t="s">
-        <v>18</v>
+      <c r="A16" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>16</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D16" s="4">
         <v>0</v>
@@ -2496,11 +2522,11 @@
       </c>
     </row>
     <row r="17" spans="1:35" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="12" t="s">
-        <v>6</v>
+      <c r="A17" s="31" t="s">
+        <v>45</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>4</v>
@@ -2603,11 +2629,11 @@
       </c>
     </row>
     <row r="18" spans="1:35" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>17</v>
+      <c r="A18" s="32" t="s">
+        <v>46</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>4</v>
@@ -2710,110 +2736,110 @@
       </c>
     </row>
     <row r="19" spans="1:35" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>12</v>
+      <c r="A19" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>10</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D19" s="13">
-        <v>0</v>
-      </c>
-      <c r="E19" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F19" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="G19" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="H19" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="I19" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J19" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="K19" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="L19" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="M19" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="N19" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="O19" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="P19" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q19" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="R19" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="S19" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="T19" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="U19" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="V19" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="W19" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="X19" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="Y19" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="Z19" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="AA19" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="AB19" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="AC19" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD19" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="AE19" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="AF19" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG19" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="AH19" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="AI19" s="14" t="s">
-        <v>18</v>
+        <v>11</v>
+      </c>
+      <c r="D19" s="11">
+        <v>0</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="F19" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="G19" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H19" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I19" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="J19" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="K19" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="L19" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="M19" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="N19" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="O19" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="P19" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q19" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="R19" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="S19" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="T19" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="U19" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="V19" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="W19" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="X19" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y19" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z19" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA19" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB19" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC19" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD19" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="AE19" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="AF19" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG19" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH19" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="AI19" s="12" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -2836,7 +2862,7 @@
         <v>2</v>
       </c>
       <c r="B1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
@@ -2939,11 +2965,11 @@
       </c>
     </row>
     <row r="2" spans="1:35" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="18" t="s">
-        <v>18</v>
+      <c r="B2" s="16" t="s">
+        <v>16</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>4</v>
@@ -3046,118 +3072,118 @@
       </c>
     </row>
     <row r="3" spans="1:35" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" s="20" t="s">
+      <c r="A3" s="17" t="s">
         <v>18</v>
       </c>
+      <c r="B3" s="18" t="s">
+        <v>16</v>
+      </c>
       <c r="C3" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="S3" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="T3" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="U3" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="V3" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="W3" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="X3" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Y3" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Z3" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AA3" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AB3" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AC3" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AD3" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AE3" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AF3" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AG3" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AH3" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AI3" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:35" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="6" t="s">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>4</v>
@@ -3261,10 +3287,10 @@
     </row>
     <row r="5" spans="1:35" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="6" t="s">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>4</v>
@@ -3367,11 +3393,11 @@
       </c>
     </row>
     <row r="6" spans="1:35" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>23</v>
+      <c r="A6" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>21</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>4</v>
@@ -3474,11 +3500,11 @@
       </c>
     </row>
     <row r="7" spans="1:35" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>24</v>
+      <c r="A7" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>22</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>4</v>
@@ -3581,332 +3607,332 @@
       </c>
     </row>
     <row r="8" spans="1:35" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>25</v>
+      <c r="A8" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" s="10">
+        <v>11</v>
+      </c>
+      <c r="D8" s="9">
         <v>0</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L8" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M8" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N8" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O8" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="P8" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q8" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="R8" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="S8" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="T8" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="U8" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="V8" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="W8" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="X8" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Y8" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Z8" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AA8" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AB8" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AC8" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AD8" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AE8" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AF8" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AG8" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AH8" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AI8" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:35" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>26</v>
+      <c r="A9" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9" s="10">
+        <v>11</v>
+      </c>
+      <c r="D9" s="9">
         <v>0</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L9" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M9" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N9" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O9" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="P9" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q9" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="R9" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="S9" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="T9" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="U9" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="V9" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="W9" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="X9" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Y9" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Z9" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AA9" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AB9" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AC9" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AD9" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AE9" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AF9" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AG9" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AH9" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AI9" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:35" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10" s="20" t="s">
-        <v>18</v>
+      <c r="A10" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>16</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="S10" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="T10" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="U10" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="V10" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="W10" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="X10" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Y10" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Z10" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AA10" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AB10" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AC10" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AD10" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AE10" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AF10" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AG10" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AH10" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AI10" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:35" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="6" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>4</v>
@@ -4010,10 +4036,10 @@
     </row>
     <row r="12" spans="1:35" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="6" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>4</v>
@@ -4116,11 +4142,11 @@
       </c>
     </row>
     <row r="13" spans="1:35" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>23</v>
+      <c r="A13" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>21</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>4</v>
@@ -4223,11 +4249,11 @@
       </c>
     </row>
     <row r="14" spans="1:35" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>24</v>
+      <c r="A14" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>22</v>
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="4"/>
@@ -4264,11 +4290,11 @@
       <c r="AI14" s="4"/>
     </row>
     <row r="15" spans="1:35" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>28</v>
+      <c r="A15" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>26</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>4</v>
@@ -4371,110 +4397,107 @@
       </c>
     </row>
     <row r="16" spans="1:35" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>12</v>
+      <c r="B16" s="7" t="s">
+        <v>10</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D16" s="10">
+        <v>11</v>
+      </c>
+      <c r="D16" s="9">
         <v>0</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L16" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M16" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N16" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O16" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="P16" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q16" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="R16" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="S16" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="T16" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="U16" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="V16" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="W16" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="X16" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Y16" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Z16" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AA16" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AB16" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AC16" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AD16" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AE16" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AF16" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AG16" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AH16" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AI16" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -4497,7 +4520,7 @@
         <v>2</v>
       </c>
       <c r="B1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
@@ -4600,11 +4623,11 @@
       </c>
     </row>
     <row r="2" spans="1:35" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="B2" s="25" t="s">
-        <v>30</v>
+      <c r="A2" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="22" t="s">
+        <v>28</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>4</v>
@@ -4707,11 +4730,11 @@
       </c>
     </row>
     <row r="3" spans="1:35" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="26" t="s">
-        <v>31</v>
-      </c>
-      <c r="B3" s="27" t="s">
-        <v>30</v>
+      <c r="A3" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="24" t="s">
+        <v>28</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>4</v>
@@ -4814,11 +4837,11 @@
       </c>
     </row>
     <row r="4" spans="1:35" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="B4" s="29" t="s">
-        <v>33</v>
+      <c r="A4" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="26" t="s">
+        <v>31</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>4</v>
@@ -4921,11 +4944,11 @@
       </c>
     </row>
     <row r="5" spans="1:35" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="B5" s="30" t="s">
+      <c r="A5" s="25" t="s">
         <v>30</v>
+      </c>
+      <c r="B5" s="27" t="s">
+        <v>28</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>4</v>
@@ -5028,11 +5051,11 @@
       </c>
     </row>
     <row r="6" spans="1:35" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" s="29" t="s">
-        <v>33</v>
+      <c r="A6" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="26" t="s">
+        <v>31</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>4</v>
@@ -5135,11 +5158,11 @@
       </c>
     </row>
     <row r="7" spans="1:35" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="B7" s="30" t="s">
-        <v>30</v>
+      <c r="A7" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="27" t="s">
+        <v>28</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>4</v>
@@ -5242,11 +5265,11 @@
       </c>
     </row>
     <row r="8" spans="1:35" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="B8" s="27" t="s">
+      <c r="A8" s="23" t="s">
         <v>33</v>
+      </c>
+      <c r="B8" s="24" t="s">
+        <v>31</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>4</v>
@@ -5349,11 +5372,11 @@
       </c>
     </row>
     <row r="9" spans="1:35" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="B9" s="29" t="s">
-        <v>33</v>
+      <c r="A9" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="26" t="s">
+        <v>31</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>4</v>
@@ -5456,11 +5479,11 @@
       </c>
     </row>
     <row r="10" spans="1:35" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="B10" s="30" t="s">
-        <v>30</v>
+      <c r="A10" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" s="27" t="s">
+        <v>28</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>4</v>
@@ -5563,11 +5586,11 @@
       </c>
     </row>
     <row r="11" spans="1:35" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="26" t="s">
-        <v>37</v>
-      </c>
-      <c r="B11" s="27" t="s">
-        <v>30</v>
+      <c r="A11" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="24" t="s">
+        <v>28</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>4</v>
@@ -5670,11 +5693,11 @@
       </c>
     </row>
     <row r="12" spans="1:35" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="31" t="s">
-        <v>38</v>
-      </c>
-      <c r="B12" s="29" t="s">
-        <v>33</v>
+      <c r="A12" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" s="26" t="s">
+        <v>31</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>4</v>
@@ -5777,11 +5800,11 @@
       </c>
     </row>
     <row r="13" spans="1:35" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="31" t="s">
-        <v>38</v>
-      </c>
-      <c r="B13" s="30" t="s">
-        <v>30</v>
+      <c r="A13" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" s="27" t="s">
+        <v>28</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>4</v>
@@ -5884,7 +5907,7 @@
       </c>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B18" s="32"/>
+      <c r="B18" s="29"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/backend/technoeconomic-inputs/technoeconomic-inputs-template.xlsx
+++ b/backend/technoeconomic-inputs/technoeconomic-inputs-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8954da175e61d5af/Escritorio/IIT/NICCP-AI/backend/technoeconomic-inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="56" documentId="10_ncr:20000_{4F2B366B-AA2F-4F18-863E-957538EF6F0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F4AD43A5-47E6-4B40-8048-7A32343975FD}"/>
+  <xr:revisionPtr revIDLastSave="65" documentId="10_ncr:20000_{4F2B366B-AA2F-4F18-863E-957538EF6F0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{32BF4B22-4E42-44BC-BDC6-3DEBC3125F0E}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Electricity" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="54">
   <si>
     <t>Units</t>
   </si>
@@ -175,16 +175,31 @@
     <t>CAPEX - OFF GRID</t>
   </si>
   <si>
-    <t>CAPEX - Heat</t>
-  </si>
-  <si>
-    <t>OPEX - Heat</t>
-  </si>
-  <si>
     <t>CAPEX - UPSTREAM</t>
   </si>
   <si>
     <t>OPEX - UPSTREAM</t>
+  </si>
+  <si>
+    <t>GRID</t>
+  </si>
+  <si>
+    <t>OFF GRID</t>
+  </si>
+  <si>
+    <t>LOCAL</t>
+  </si>
+  <si>
+    <t>UPSTREAM</t>
+  </si>
+  <si>
+    <t>CAPEX - HEAT</t>
+  </si>
+  <si>
+    <t>OPEX - HEAT</t>
+  </si>
+  <si>
+    <t>HEAT</t>
   </si>
 </sst>
 </file>
@@ -421,7 +436,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -520,6 +535,9 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -536,6 +554,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1560,7 +1582,7 @@
     </row>
     <row r="8" spans="1:35" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="8" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>10</v>
@@ -2202,7 +2224,7 @@
     </row>
     <row r="14" spans="1:35" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="13" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>10</v>
@@ -2523,7 +2545,7 @@
     </row>
     <row r="17" spans="1:35" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="31" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>14</v>
@@ -2630,7 +2652,7 @@
     </row>
     <row r="18" spans="1:35" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="32" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>15</v>
@@ -2737,7 +2759,7 @@
     </row>
     <row r="19" spans="1:35" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="14" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>10</v>
@@ -3608,7 +3630,7 @@
     </row>
     <row r="8" spans="1:35" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="8" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>23</v>
@@ -3715,7 +3737,7 @@
     </row>
     <row r="9" spans="1:35" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="13" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>24</v>
@@ -3929,7 +3951,7 @@
     </row>
     <row r="11" spans="1:35" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>19</v>
@@ -4036,7 +4058,7 @@
     </row>
     <row r="12" spans="1:35" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>20</v>
@@ -4143,7 +4165,7 @@
     </row>
     <row r="13" spans="1:35" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="7" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>21</v>
@@ -4250,7 +4272,7 @@
     </row>
     <row r="14" spans="1:35" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="7" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>22</v>
@@ -4291,7 +4313,7 @@
     </row>
     <row r="15" spans="1:35" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="7" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>26</v>
@@ -4397,6 +4419,9 @@
       </c>
     </row>
     <row r="16" spans="1:35" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="33" t="s">
+        <v>50</v>
+      </c>
       <c r="B16" s="7" t="s">
         <v>10</v>
       </c>
